--- a/SGC-CKN/Excel/e7b779a7-bffd-413a-bde0-5b218b52ccec_Cọc_khoan_nhồi_2_11-15_D800_26-03-2026.xlsx
+++ b/SGC-CKN/Excel/e7b779a7-bffd-413a-bde0-5b218b52ccec_Cọc_khoan_nhồi_2_11-15_D800_26-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>2.11-15</t>
+    <t>P11-150</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
